--- a/ig/main/ValueSet-allergie.xlsx
+++ b/ig/main/ValueSet-allergie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T16:45:55+00:00</t>
+    <t>2024-10-27T04:29:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-allergie.xlsx
+++ b/ig/main/ValueSet-allergie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-27T04:29:11+00:00</t>
+    <t>2024-10-27T10:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
